--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VVSS\docs\Lab02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UBB an 3 sem 2\VVSS\docs\Lab02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0364BFF6-0F46-4A55-A719-813E965510C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC40AE1-B07D-4464-BA0F-9771E686C9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,20 @@
     <sheet name="F01.BVA" sheetId="3" r:id="rId3"/>
     <sheet name="BBT-TCs" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -90,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="125">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -323,129 +336,9 @@
     <t>Executable</t>
   </si>
   <si>
-    <t>titlu is String, length in [1,255]</t>
-  </si>
-  <si>
-    <t>01. titlu = "", length = 0</t>
-  </si>
-  <si>
-    <t>titlu</t>
-  </si>
-  <si>
-    <t>regizor</t>
-  </si>
-  <si>
-    <t>an aparitie</t>
-  </si>
-  <si>
-    <t>actori</t>
-  </si>
-  <si>
-    <t>cuvinte cheie</t>
-  </si>
-  <si>
     <t>expected result</t>
   </si>
   <si>
-    <t>02. titlu = ?, length = -1</t>
-  </si>
-  <si>
-    <t>TC3_EC</t>
-  </si>
-  <si>
-    <t>03. titlu = "M", length = 1</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>…</t>
-  </si>
-  <si>
-    <t>Error message-? Compiler checked</t>
-  </si>
-  <si>
-    <t>04. titlu = "M…123", length = 255</t>
-  </si>
-  <si>
-    <t>"M"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Director1, Director 2</t>
-  </si>
-  <si>
-    <t>Actor1, Actor2</t>
-  </si>
-  <si>
-    <t>Drama</t>
-  </si>
-  <si>
-    <t>keyword1, keyword2</t>
-  </si>
-  <si>
-    <t>record added</t>
-  </si>
-  <si>
-    <t>05. titlu = "M…12", length = 254</t>
-  </si>
-  <si>
-    <t>"M…123"</t>
-  </si>
-  <si>
-    <t>06. titlu = "M…1234", length = 256</t>
-  </si>
-  <si>
-    <t>"M…12"</t>
-  </si>
-  <si>
-    <t>regizor is String, length in [1,255]</t>
-  </si>
-  <si>
-    <t>07. regizor = "", length = 0</t>
-  </si>
-  <si>
-    <t>"M…1234"</t>
-  </si>
-  <si>
-    <t>08. regizor = ?, length = -1</t>
-  </si>
-  <si>
-    <t>09. regizor = "D", length = 1</t>
-  </si>
-  <si>
-    <t>10. regizor = "D…123", length = 255</t>
-  </si>
-  <si>
-    <t>11. regizor = "D…12", length = 254</t>
-  </si>
-  <si>
-    <t>12. regizor = "D…1234", length = 256</t>
-  </si>
-  <si>
-    <t>an aparitie &gt;1900</t>
-  </si>
-  <si>
-    <t>13. an = 1960</t>
-  </si>
-  <si>
-    <t>14. an = 1959</t>
-  </si>
-  <si>
-    <t>15. an = 1961</t>
-  </si>
-  <si>
-    <t>16. an = max - 1</t>
-  </si>
-  <si>
-    <t>17. an = max + 1</t>
-  </si>
-  <si>
-    <t>18. an = max</t>
-  </si>
-  <si>
     <t>BBT TCs</t>
   </si>
   <si>
@@ -525,6 +418,66 @@
   </si>
   <si>
     <t>not yet</t>
+  </si>
+  <si>
+    <t>nume is String, length &gt;= 1</t>
+  </si>
+  <si>
+    <t>01. nume = "", length = 0</t>
+  </si>
+  <si>
+    <t>02. nume = "A", length = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03. nume = "AB", length = 2 </t>
+  </si>
+  <si>
+    <t>04. pret = -0.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05. pret = 0.0 </t>
+  </si>
+  <si>
+    <t>06. pret = 0.01</t>
+  </si>
+  <si>
+    <t>07. pret = 1.0</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>TC3_BVA</t>
+  </si>
+  <si>
+    <t>TC4_BVA</t>
+  </si>
+  <si>
+    <t>TC5_BVA</t>
+  </si>
+  <si>
+    <t>TC6_BVA</t>
+  </si>
+  <si>
+    <t>TC7_BVA</t>
+  </si>
+  <si>
+    <t>JUICE</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>Espresso</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CLASSIC_COFFEE</t>
+  </si>
+  <si>
+    <t>Produs adăugat cu succes</t>
   </si>
 </sst>
 </file>
@@ -1179,16 +1132,30 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1196,56 +1163,42 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1555,36 +1508,36 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
-    <col min="9" max="9" width="32.85546875" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.88671875" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C1" s="76" t="s">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="78"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
       <c r="H1" s="49" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="49"/>
       <c r="J1" s="49"/>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="79" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H2" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="77"/>
-      <c r="J2" s="78"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I2" s="79"/>
+      <c r="J2" s="80"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
         <v>3</v>
@@ -1593,21 +1546,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="35"/>
       <c r="H6" s="2" t="s">
         <v>7</v>
@@ -1615,40 +1568,40 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="47" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>12</v>
       </c>
@@ -1656,7 +1609,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>13</v>
       </c>
@@ -1664,7 +1617,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>14</v>
       </c>
@@ -1672,32 +1625,32 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B18" s="47" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C20" s="45" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
@@ -1714,7 +1667,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
@@ -1731,25 +1684,25 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="46"/>
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="75"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
-      <c r="J24" s="75"/>
-      <c r="K24" s="75"/>
-      <c r="L24" s="75"/>
-      <c r="M24" s="75"/>
-      <c r="N24" s="75"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C24" s="90"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="90"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="90"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="90"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C26" s="48"/>
     </row>
   </sheetData>
@@ -1769,37 +1722,37 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:Q24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" customWidth="1"/>
-    <col min="4" max="4" width="60.7109375" customWidth="1"/>
-    <col min="5" max="5" width="45.7109375" customWidth="1"/>
-    <col min="6" max="6" width="5.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.6640625" customWidth="1"/>
+    <col min="4" max="4" width="60.6640625" customWidth="1"/>
+    <col min="5" max="5" width="45.6640625" customWidth="1"/>
+    <col min="6" max="6" width="5.88671875" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="18.5703125" customWidth="1"/>
-    <col min="16" max="16" width="49.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="18.5546875" customWidth="1"/>
+    <col min="16" max="16" width="49.5546875" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="I1" s="86" t="s">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="I1" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="77"/>
-      <c r="K1" s="78"/>
-    </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B2" s="76" t="s">
+      <c r="J1" s="79"/>
+      <c r="K1" s="80"/>
+    </row>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B2" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="78"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="80"/>
       <c r="I2" s="59"/>
       <c r="J2" s="59" t="s">
         <v>3</v>
@@ -1808,7 +1761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="I3" s="59" t="s">
         <v>5</v>
       </c>
@@ -1819,15 +1772,15 @@
         <v>234</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="87" t="s">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B4" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="78"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="80"/>
       <c r="I4" s="59" t="s">
         <v>6</v>
       </c>
@@ -1838,7 +1791,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="I5" s="59" t="s">
         <v>7</v>
       </c>
@@ -1849,35 +1802,35 @@
         <v>234</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="H6" s="60"/>
       <c r="I6" s="59"/>
       <c r="J6" s="59"/>
       <c r="K6" s="59"/>
       <c r="L6" s="60"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="88" t="s">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="78"/>
-      <c r="G7" s="85" t="s">
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="80"/>
+      <c r="G7" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="97"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="97"/>
-      <c r="M7" s="97"/>
-      <c r="N7" s="97"/>
-      <c r="O7" s="97"/>
-      <c r="P7" s="97"/>
-      <c r="Q7" s="98"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="75"/>
+      <c r="Q7" s="76"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="21" t="s">
         <v>28</v>
       </c>
@@ -1890,39 +1843,39 @@
       <c r="E8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="84" t="s">
+      <c r="G8" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="83" t="s">
+      <c r="H8" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="83" t="s">
+      <c r="I8" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="97"/>
-      <c r="K8" s="97"/>
-      <c r="L8" s="97"/>
-      <c r="M8" s="97"/>
-      <c r="N8" s="97"/>
-      <c r="O8" s="98"/>
-      <c r="P8" s="83" t="s">
+      <c r="J8" s="75"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="75"/>
+      <c r="M8" s="75"/>
+      <c r="N8" s="75"/>
+      <c r="O8" s="76"/>
+      <c r="P8" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="Q8" s="98"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q8" s="76"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>1</v>
       </c>
-      <c r="C9" s="80" t="s">
+      <c r="C9" s="84" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>37</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
       <c r="I9" s="21" t="s">
         <v>38</v>
       </c>
@@ -1945,11 +1898,11 @@
       </c>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>2</v>
       </c>
-      <c r="C10" s="81"/>
+      <c r="C10" s="85"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>44</v>
@@ -1982,11 +1935,11 @@
       </c>
       <c r="Q10" s="3"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>3</v>
       </c>
-      <c r="C11" s="81"/>
+      <c r="C11" s="85"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
         <v>50</v>
@@ -2019,11 +1972,11 @@
       </c>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>4</v>
       </c>
-      <c r="C12" s="82"/>
+      <c r="C12" s="86"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>56</v>
@@ -2056,11 +2009,11 @@
       </c>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>5</v>
       </c>
-      <c r="C13" s="80" t="s">
+      <c r="C13" s="84" t="s">
         <v>60</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -2095,11 +2048,11 @@
       </c>
       <c r="Q13" s="3"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
         <v>6</v>
       </c>
-      <c r="C14" s="81"/>
+      <c r="C14" s="85"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>67</v>
@@ -2116,11 +2069,11 @@
       <c r="P14" s="64"/>
       <c r="Q14" s="3"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
         <v>7</v>
       </c>
-      <c r="C15" s="82"/>
+      <c r="C15" s="86"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
         <v>68</v>
@@ -2137,7 +2090,7 @@
       <c r="P15" s="64"/>
       <c r="Q15" s="3"/>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -2153,7 +2106,7 @@
       <c r="P16" s="19"/>
       <c r="Q16" s="3"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -2170,7 +2123,7 @@
       <c r="P17" s="19"/>
       <c r="Q17" s="3"/>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -2186,7 +2139,7 @@
       <c r="P18" s="19"/>
       <c r="Q18" s="3"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -2203,7 +2156,7 @@
       <c r="P19" s="19"/>
       <c r="Q19" s="3"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -2219,7 +2172,7 @@
       <c r="P20" s="19"/>
       <c r="Q20" s="3"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -2236,12 +2189,12 @@
       <c r="P21" s="19"/>
       <c r="Q21" s="3"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
         <v>69</v>
       </c>
@@ -2249,17 +2202,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="I8:O8"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="G8:G9"/>
     <mergeCell ref="G7:Q7"/>
     <mergeCell ref="P8:Q8"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="I8:O8"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="G8:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2270,41 +2223,40 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:R32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:Q32"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.28515625" customWidth="1"/>
-    <col min="18" max="18" width="9.42578125" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5546875" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.33203125" customWidth="1"/>
+    <col min="17" max="17" width="9.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="K1" s="86" t="s">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="K1" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="77"/>
-      <c r="M1" s="78"/>
-    </row>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B2" s="76" t="s">
+      <c r="L1" s="79"/>
+      <c r="M1" s="80"/>
+    </row>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B2" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="78"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="80"/>
       <c r="K2" s="59"/>
       <c r="L2" s="59" t="s">
         <v>3</v>
@@ -2313,7 +2265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="K3" s="59" t="s">
         <v>5</v>
       </c>
@@ -2324,15 +2276,15 @@
         <v>234</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B4" s="87" t="s">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B4" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="78"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="80"/>
       <c r="K4" s="59" t="s">
         <v>6</v>
       </c>
@@ -2343,7 +2295,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="61"/>
       <c r="C5" s="61"/>
       <c r="D5" s="61"/>
@@ -2360,29 +2312,28 @@
         <v>234</v>
       </c>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B7" s="95" t="s">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="78"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="80"/>
       <c r="E7" s="3"/>
-      <c r="G7" s="85" t="s">
+      <c r="G7" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="77"/>
-      <c r="L7" s="77"/>
-      <c r="M7" s="77"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="78"/>
-    </row>
-    <row r="8" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="79"/>
+      <c r="N7" s="79"/>
+      <c r="O7" s="79"/>
+      <c r="P7" s="79"/>
+      <c r="Q7" s="80"/>
+    </row>
+    <row r="8" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>72</v>
       </c>
@@ -2393,73 +2344,69 @@
         <v>70</v>
       </c>
       <c r="E8" s="9"/>
-      <c r="G8" s="84" t="s">
+      <c r="G8" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="H8" s="84" t="s">
+      <c r="H8" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="84" t="s">
+      <c r="I8" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="J8" s="83" t="s">
+      <c r="J8" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="K8" s="91" t="s">
+      <c r="K8" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="L8" s="77"/>
-      <c r="M8" s="77"/>
-      <c r="N8" s="77"/>
-      <c r="O8" s="77"/>
-      <c r="P8" s="78"/>
-      <c r="Q8" s="91" t="s">
+      <c r="L8" s="79"/>
+      <c r="M8" s="79"/>
+      <c r="N8" s="79"/>
+      <c r="O8" s="79"/>
+      <c r="P8" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="78"/>
-    </row>
-    <row r="9" spans="2:18" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="80">
+      <c r="Q8" s="80"/>
+    </row>
+    <row r="9" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="84">
         <v>1</v>
       </c>
-      <c r="C9" s="92" t="s">
+      <c r="C9" s="93" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="O9" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="M9" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="N9" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="O9" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="P9" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q9" s="83" t="s">
-        <v>84</v>
-      </c>
-      <c r="R9" s="78"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
+      <c r="Q9" s="80"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
       <c r="D10" s="2" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="G10" s="21">
         <v>1</v>
@@ -2468,23 +2415,34 @@
         <v>1</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="14"/>
-      <c r="K10" s="32"/>
+        <v>118</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="K10" s="31">
+        <v>7</v>
+      </c>
       <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="89"/>
-      <c r="R10" s="78"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="81"/>
-      <c r="C11" s="81"/>
+      <c r="M10" s="32">
+        <v>10</v>
+      </c>
+      <c r="N10" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="O10" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" s="92" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q10" s="80"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
       <c r="D11" s="2" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="G11" s="17">
         <v>2</v>
@@ -2492,151 +2450,149 @@
       <c r="H11" s="18">
         <v>2</v>
       </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="K11" s="20" t="s">
-        <v>89</v>
+      <c r="I11" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="K11" s="20">
+        <v>5</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="N11" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="M11" s="16">
+        <v>10</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="O11" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q11" s="94" t="s">
-        <v>91</v>
-      </c>
-      <c r="R11" s="78"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="81"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="P11" s="95" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q11" s="80"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B12" s="85"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="2"/>
       <c r="G12" s="21">
         <v>3</v>
       </c>
       <c r="H12" s="15">
         <v>3</v>
       </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="31" t="s">
-        <v>93</v>
+      <c r="I12" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="K12" s="31">
+        <v>6</v>
       </c>
       <c r="L12" s="32" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="M12" s="32">
-        <v>2010</v>
+        <v>10</v>
       </c>
       <c r="N12" s="32" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="O12" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="P12" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q12" s="89" t="s">
-        <v>98</v>
-      </c>
-      <c r="R12" s="78"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="81"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="2" t="s">
-        <v>99</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="P12" s="95" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q12" s="80"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B13" s="85"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="2"/>
       <c r="G13" s="21">
         <v>4</v>
       </c>
       <c r="H13" s="15">
         <v>4</v>
       </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="31" t="s">
-        <v>100</v>
+      <c r="I13" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="K13" s="31">
+        <v>3</v>
       </c>
       <c r="L13" s="32" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="M13" s="32">
-        <v>2010</v>
+        <v>-0.01</v>
       </c>
       <c r="N13" s="32" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="O13" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="P13" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q13" s="89" t="s">
-        <v>98</v>
-      </c>
-      <c r="R13" s="78"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="82"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="2" t="s">
-        <v>101</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="P13" s="92" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q13" s="80"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="2"/>
       <c r="G14" s="21">
         <v>5</v>
       </c>
       <c r="H14" s="15">
         <v>5</v>
       </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="31" t="s">
-        <v>102</v>
+      <c r="I14" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="K14" s="31">
+        <v>2</v>
       </c>
       <c r="L14" s="32" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="M14" s="32">
-        <v>2010</v>
+        <v>0</v>
       </c>
       <c r="N14" s="32" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="O14" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="P14" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q14" s="89" t="s">
-        <v>98</v>
-      </c>
-      <c r="R14" s="78"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="80">
+        <v>54</v>
+      </c>
+      <c r="P14" s="92" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q14" s="80"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B15" s="84">
         <v>2</v>
       </c>
-      <c r="C15" s="80" t="s">
-        <v>103</v>
+      <c r="C15" s="84" t="s">
+        <v>60</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G15" s="17">
         <v>6</v>
@@ -2644,38 +2600,37 @@
       <c r="H15" s="18">
         <v>6</v>
       </c>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>105</v>
+      <c r="I15" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="K15" s="20">
+        <v>1</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="M15" s="16">
-        <v>2010</v>
+        <v>0.01</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="O15" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="P15" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q15" s="94" t="s">
-        <v>91</v>
-      </c>
-      <c r="R15" s="78"/>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="81"/>
-      <c r="C16" s="81"/>
+        <v>54</v>
+      </c>
+      <c r="P15" s="95" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q15" s="80"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B16" s="85"/>
+      <c r="C16" s="85"/>
       <c r="D16" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G16" s="21">
         <v>7</v>
@@ -2684,52 +2639,56 @@
         <v>7</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="89"/>
-      <c r="R16" s="78"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="81"/>
-      <c r="C17" s="81"/>
+        <v>113</v>
+      </c>
+      <c r="K16" s="31">
+        <v>4</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="M16" s="32">
+        <v>1</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="P16" s="95" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q16" s="80"/>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B17" s="85"/>
+      <c r="C17" s="85"/>
       <c r="D17" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G17" s="21">
         <v>8</v>
       </c>
-      <c r="H17" s="15">
-        <v>8</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>90</v>
-      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
       <c r="K17" s="32"/>
       <c r="L17" s="32"/>
       <c r="M17" s="32"/>
       <c r="N17" s="32"/>
       <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="89"/>
-      <c r="R17" s="78"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="81"/>
-      <c r="C18" s="81"/>
+      <c r="P17" s="92"/>
+      <c r="Q17" s="80"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B18" s="85"/>
+      <c r="C18" s="85"/>
       <c r="D18" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G18" s="21">
         <v>9</v>
@@ -2742,16 +2701,13 @@
       <c r="M18" s="32"/>
       <c r="N18" s="32"/>
       <c r="O18" s="32"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="89"/>
-      <c r="R18" s="78"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="81"/>
-      <c r="C19" s="81"/>
-      <c r="D19" s="2" t="s">
-        <v>109</v>
-      </c>
+      <c r="P18" s="92"/>
+      <c r="Q18" s="80"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B19" s="85"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="2"/>
       <c r="G19" s="21">
         <v>10</v>
       </c>
@@ -2763,16 +2719,13 @@
       <c r="M19" s="32"/>
       <c r="N19" s="32"/>
       <c r="O19" s="32"/>
-      <c r="P19" s="32"/>
-      <c r="Q19" s="89"/>
-      <c r="R19" s="78"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="2" t="s">
-        <v>110</v>
-      </c>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="80"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="2"/>
       <c r="G20" s="21">
         <v>11</v>
       </c>
@@ -2784,20 +2737,13 @@
       <c r="M20" s="32"/>
       <c r="N20" s="32"/>
       <c r="O20" s="32"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="89"/>
-      <c r="R20" s="78"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="80">
-        <v>3</v>
-      </c>
-      <c r="C21" s="92" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>112</v>
-      </c>
+      <c r="P20" s="92"/>
+      <c r="Q20" s="80"/>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B21" s="84"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="2"/>
       <c r="G21" s="21">
         <v>12</v>
       </c>
@@ -2809,16 +2755,13 @@
       <c r="M21" s="32"/>
       <c r="N21" s="32"/>
       <c r="O21" s="32"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="89"/>
-      <c r="R21" s="78"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="81"/>
-      <c r="C22" s="81"/>
-      <c r="D22" s="2" t="s">
-        <v>113</v>
-      </c>
+      <c r="P21" s="92"/>
+      <c r="Q21" s="80"/>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B22" s="85"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="2"/>
       <c r="G22" s="21">
         <v>13</v>
       </c>
@@ -2830,16 +2773,13 @@
       <c r="M22" s="32"/>
       <c r="N22" s="32"/>
       <c r="O22" s="32"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="89"/>
-      <c r="R22" s="78"/>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="81"/>
-      <c r="C23" s="81"/>
-      <c r="D23" s="2" t="s">
-        <v>114</v>
-      </c>
+      <c r="P22" s="92"/>
+      <c r="Q22" s="80"/>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B23" s="85"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="2"/>
       <c r="G23" s="21">
         <v>14</v>
       </c>
@@ -2851,16 +2791,13 @@
       <c r="M23" s="32"/>
       <c r="N23" s="32"/>
       <c r="O23" s="32"/>
-      <c r="P23" s="32"/>
-      <c r="Q23" s="89"/>
-      <c r="R23" s="78"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="81"/>
-      <c r="C24" s="81"/>
-      <c r="D24" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="P23" s="92"/>
+      <c r="Q23" s="80"/>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B24" s="85"/>
+      <c r="C24" s="85"/>
+      <c r="D24" s="2"/>
       <c r="G24" s="21">
         <v>15</v>
       </c>
@@ -2872,16 +2809,13 @@
       <c r="M24" s="32"/>
       <c r="N24" s="32"/>
       <c r="O24" s="32"/>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="89"/>
-      <c r="R24" s="78"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="81"/>
-      <c r="C25" s="81"/>
-      <c r="D25" s="2" t="s">
-        <v>116</v>
-      </c>
+      <c r="P24" s="92"/>
+      <c r="Q24" s="80"/>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B25" s="85"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="2"/>
       <c r="G25" s="21">
         <v>16</v>
       </c>
@@ -2893,16 +2827,13 @@
       <c r="M25" s="32"/>
       <c r="N25" s="32"/>
       <c r="O25" s="32"/>
-      <c r="P25" s="32"/>
-      <c r="Q25" s="89"/>
-      <c r="R25" s="78"/>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="82"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="2" t="s">
-        <v>117</v>
-      </c>
+      <c r="P25" s="92"/>
+      <c r="Q25" s="80"/>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B26" s="86"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="2"/>
       <c r="G26" s="21">
         <v>17</v>
       </c>
@@ -2914,20 +2845,13 @@
       <c r="M26" s="32"/>
       <c r="N26" s="32"/>
       <c r="O26" s="32"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="89"/>
-      <c r="R26" s="78"/>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="80">
-        <v>4</v>
-      </c>
-      <c r="C27" s="92" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>90</v>
-      </c>
+      <c r="P26" s="92"/>
+      <c r="Q26" s="80"/>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B27" s="84"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="2"/>
       <c r="G27" s="21">
         <v>18</v>
       </c>
@@ -2939,102 +2863,91 @@
       <c r="M27" s="32"/>
       <c r="N27" s="32"/>
       <c r="O27" s="32"/>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="89"/>
-      <c r="R27" s="78"/>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="81"/>
-      <c r="C28" s="81"/>
-      <c r="D28" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="81"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="81"/>
-      <c r="C30" s="81"/>
-      <c r="D30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G30" s="93"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="90"/>
-      <c r="J30" s="75"/>
-      <c r="K30" s="75"/>
-      <c r="L30" s="75"/>
-      <c r="M30" s="75"/>
+      <c r="P27" s="92"/>
+      <c r="Q27" s="80"/>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B28" s="85"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B29" s="85"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B30" s="85"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="2"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="99"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="90"/>
       <c r="N30" s="41"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B31" s="81"/>
-      <c r="C31" s="81"/>
-      <c r="D31" s="2" t="s">
-        <v>90</v>
-      </c>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B31" s="85"/>
+      <c r="C31" s="85"/>
+      <c r="D31" s="2"/>
       <c r="I31" s="96"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="75"/>
-      <c r="M31" s="75"/>
+      <c r="J31" s="90"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="90"/>
+      <c r="M31" s="90"/>
       <c r="N31" s="42"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="2" t="s">
-        <v>90</v>
-      </c>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="I30:M30"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="C15:C20"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P27:Q27"/>
     <mergeCell ref="C27:C32"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B15:B20"/>
     <mergeCell ref="B9:B14"/>
-    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="P17:Q17"/>
     <mergeCell ref="H8:H9"/>
-    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="P11:Q11"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="I31:M31"/>
-    <mergeCell ref="G7:R7"/>
+    <mergeCell ref="G7:Q7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="G30:H30"/>
-    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="P15:Q15"/>
     <mergeCell ref="C21:C26"/>
     <mergeCell ref="B27:B32"/>
-    <mergeCell ref="K8:P8"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="K8:O8"/>
     <mergeCell ref="B21:B26"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P26:Q26"/>
     <mergeCell ref="C9:C14"/>
     <mergeCell ref="G8:G9"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="C15:C20"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="I30:M30"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="P12:Q12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3048,26 +2961,26 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="B1:P25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" customWidth="1"/>
-    <col min="13" max="13" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" customWidth="1"/>
+    <col min="13" max="13" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H1" s="86" t="s">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="H1" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="77"/>
-      <c r="J1" s="78"/>
-    </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="I1" s="79"/>
+      <c r="J1" s="80"/>
+    </row>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" s="66" t="s">
         <v>0</v>
       </c>
@@ -3079,7 +2992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="62"/>
       <c r="C3" s="62"/>
       <c r="D3" s="62"/>
@@ -3094,7 +3007,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="62"/>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
@@ -3109,7 +3022,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" s="62"/>
       <c r="C5" s="62"/>
       <c r="D5" s="62"/>
@@ -3124,23 +3037,23 @@
         <v>234</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="58" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="67" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="C8" s="68" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>34</v>
@@ -3149,7 +3062,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F9" s="24" t="s">
         <v>38</v>
       </c>
@@ -3170,21 +3083,21 @@
         <v>43</v>
       </c>
       <c r="N9" s="24" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B10" s="22">
         <v>1</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="F10" s="27">
         <v>1</v>
@@ -3209,18 +3122,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="F11" s="8">
         <v>2</v>
@@ -3245,18 +3158,18 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="F12" s="6">
         <v>3</v>
@@ -3282,18 +3195,18 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="F13" s="11">
         <v>4</v>
@@ -3318,15 +3231,15 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <v>5</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="10"/>
@@ -3337,15 +3250,15 @@
       <c r="M14" s="6"/>
       <c r="N14" s="11"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <v>6</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="10"/>
@@ -3356,7 +3269,7 @@
       <c r="M15" s="5"/>
       <c r="N15" s="11"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="11"/>
       <c r="D16" s="29"/>
       <c r="E16" s="11"/>
@@ -3369,7 +3282,7 @@
       <c r="M16" s="5"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="23"/>
       <c r="D17" s="30"/>
       <c r="E17" s="23"/>
@@ -3382,7 +3295,7 @@
       <c r="M17" s="23"/>
       <c r="N17" s="23"/>
     </row>
-    <row r="18" spans="2:16" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:16" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B18" s="25"/>
       <c r="C18" s="25"/>
       <c r="D18" s="26"/>
@@ -3397,9 +3310,9 @@
       <c r="M18" s="25"/>
       <c r="N18" s="25"/>
     </row>
-    <row r="19" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="25" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="C19" s="25"/>
       <c r="D19" s="26"/>
@@ -3412,70 +3325,70 @@
       <c r="K19" s="3"/>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="2:16" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:16" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C21" s="53" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="M21" s="53" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="55" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="C22" s="56" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="F22" s="52" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="G22" s="57" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="H22" s="56" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="J22" s="33" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="K22" s="33" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="L22" s="52" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="M22" s="72" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="N22" s="33" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="O22" s="33" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="P22" s="52" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="40" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="C24" s="36">
         <v>8</v>
@@ -3489,7 +3402,7 @@
       <c r="F24" s="39"/>
       <c r="G24" s="44"/>
       <c r="H24" s="73" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="J24" s="2">
         <v>3</v>
@@ -3501,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="43" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="N24" s="2">
         <v>5</v>
@@ -3513,7 +3426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="M25" s="3"/>
     </row>
   </sheetData>

--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -18,7 +18,6 @@
     <sheet name="BBT-TCs" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -64,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="132">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -102,22 +101,10 @@
     <t>Informaţiile vor fi preluate din fişiere text.</t>
   </si>
   <si>
-    <t>1. Evidenţa filmelor din colecţia personală</t>
-  </si>
-  <si>
-    <t>Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
-  </si>
-  <si>
-    <t>F01. adăugarea unui film nou (titlu, regizor, an aparitie, actori, categorie, cuvinte cheie);</t>
-  </si>
-  <si>
     <t>Observații</t>
   </si>
   <si>
     <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
-  </si>
-  <si>
-    <t>addMovie(String title, String director, int year, List&lt;String&gt; actors, String category, List&lt;String&gt; keywords): void</t>
   </si>
   <si>
     <t>2. Metoda este definită la nivelul repository, service sau ui.</t>
@@ -487,6 +474,15 @@
       </rPr>
       <t>failed</t>
     </r>
+  </si>
+  <si>
+    <t>addProduct(Product p): void</t>
+  </si>
+  <si>
+    <t>1. Gestiune magazin de bauturi</t>
+  </si>
+  <si>
+    <t>F01. adăugarea unui produs nou (id, nume, pret, categorie, tip);</t>
   </si>
 </sst>
 </file>
@@ -1139,92 +1135,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1233,39 +1143,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1274,21 +1151,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1296,9 +1158,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1316,6 +1175,122 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1334,32 +1309,53 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1679,12 +1675,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="43"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="65"/>
       <c r="H1" s="25" t="s">
         <v>1</v>
       </c>
@@ -1692,11 +1688,11 @@
       <c r="J1" s="25"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="43"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H3" s="2"/>
@@ -1764,23 +1760,20 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -1793,27 +1786,27 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B18" s="23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C20" s="21" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -1830,7 +1823,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -1847,21 +1840,21 @@
     </row>
     <row r="24" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="22"/>
-      <c r="B24" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
+      <c r="B24" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="62"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="62"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="62"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C26" s="24"/>
@@ -1900,19 +1893,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="I1" s="47" t="s">
+      <c r="I1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="42"/>
-      <c r="K1" s="43"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="65"/>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="43"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
       <c r="I2" s="28"/>
       <c r="J2" s="28" t="s">
         <v>3</v>
@@ -1926,26 +1919,26 @@
         <v>5</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K3" s="28">
         <v>234</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
+      <c r="B4" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="65"/>
       <c r="I4" s="28" t="s">
         <v>6</v>
       </c>
       <c r="J4" s="28" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K4" s="28">
         <v>234</v>
@@ -1956,7 +1949,7 @@
         <v>7</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K5" s="28">
         <v>234</v>
@@ -1970,161 +1963,161 @@
       <c r="L6" s="29"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B7" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="43"/>
-      <c r="G7" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
+      <c r="B7" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="65"/>
+      <c r="G7" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="H8" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="I8" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="32" t="s">
         <v>31</v>
-      </c>
-      <c r="G8" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="32" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>1</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="L9" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="11" t="s">
+      <c r="M9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="N9" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="N9" s="11" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>2</v>
       </c>
-      <c r="C10" s="51"/>
+      <c r="C10" s="68"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G10" s="11">
         <v>1</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I10" s="26">
         <v>1</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K10" s="26">
         <v>12.5</v>
       </c>
       <c r="L10" s="26" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M10" s="26" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="N10" s="26" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>3</v>
       </c>
-      <c r="C11" s="51"/>
+      <c r="C11" s="68"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G11" s="11">
         <v>2</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I11" s="26">
         <v>2</v>
       </c>
       <c r="J11" s="26" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="K11" s="26">
         <v>10</v>
       </c>
       <c r="L11" s="26" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M11" s="26" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="N11" s="26" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>4</v>
       </c>
-      <c r="C12" s="52"/>
+      <c r="C12" s="69"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G12" s="32">
         <v>3</v>
@@ -2136,30 +2129,30 @@
         <v>3</v>
       </c>
       <c r="J12" s="33" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K12" s="33">
         <v>10</v>
       </c>
       <c r="L12" s="33" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M12" s="33" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>5</v>
       </c>
-      <c r="C13" s="50" t="s">
-        <v>59</v>
+      <c r="C13" s="67" t="s">
+        <v>55</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E13" s="4"/>
       <c r="G13" s="32">
@@ -2172,29 +2165,29 @@
         <v>4</v>
       </c>
       <c r="J13" s="33" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="K13" s="33">
         <v>10</v>
       </c>
       <c r="L13" s="33" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M13" s="33" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
         <v>6</v>
       </c>
-      <c r="C14" s="51"/>
+      <c r="C14" s="68"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
@@ -2209,10 +2202,10 @@
       <c r="B15" s="4">
         <v>7</v>
       </c>
-      <c r="C15" s="52"/>
+      <c r="C15" s="69"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
@@ -2223,22 +2216,22 @@
     </row>
     <row r="18" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F18" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="G7:N7"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B2:E2"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="I8:M8"/>
     <mergeCell ref="C9:C12"/>
     <mergeCell ref="H8:H9"/>
     <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2271,19 +2264,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="K1" s="47" t="s">
+      <c r="K1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="65"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="43"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
       <c r="K2" s="28"/>
       <c r="L2" s="28" t="s">
         <v>3</v>
@@ -2297,26 +2290,26 @@
         <v>5</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="M3" s="28">
         <v>234</v>
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B4" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
+      <c r="B4" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="65"/>
       <c r="K4" s="28" t="s">
         <v>6</v>
       </c>
       <c r="L4" s="28" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M4" s="28">
         <v>234</v>
@@ -2333,107 +2326,107 @@
         <v>7</v>
       </c>
       <c r="L5" s="28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="M5" s="28">
         <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B7" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
+      <c r="B7" s="87" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
       <c r="E7" s="3"/>
-      <c r="G7" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="43"/>
+      <c r="G7" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="65"/>
     </row>
     <row r="8" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="G8" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="70" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="G8" s="55" t="s">
+      <c r="K8" s="91" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="91" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" s="65"/>
+    </row>
+    <row r="9" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="78">
+        <v>1</v>
+      </c>
+      <c r="C9" s="81" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="P9" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" s="55" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="K8" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="57" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q8" s="43"/>
-    </row>
-    <row r="9" spans="2:17" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="65">
-        <v>1</v>
-      </c>
-      <c r="C9" s="68" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="O9" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="P9" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q9" s="43"/>
+      <c r="Q9" s="65"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="66"/>
-      <c r="C10" s="69"/>
+      <c r="B10" s="79"/>
+      <c r="C10" s="82"/>
       <c r="D10" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G10" s="11">
         <v>1</v>
@@ -2442,10 +2435,10 @@
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K10" s="15">
         <v>7</v>
@@ -2455,59 +2448,59 @@
         <v>10</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="P10" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q10" s="43"/>
+        <v>59</v>
+      </c>
+      <c r="P10" s="92" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q10" s="65"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="66"/>
-      <c r="C11" s="69"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="82"/>
       <c r="D11" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G11" s="35">
         <v>2</v>
       </c>
-      <c r="H11" s="72">
+      <c r="H11" s="40">
         <v>2</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J11" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="K11" s="41">
+        <v>5</v>
+      </c>
+      <c r="L11" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="J11" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="K11" s="73">
-        <v>5</v>
-      </c>
-      <c r="L11" s="74" t="s">
+      <c r="M11" s="42">
+        <v>10</v>
+      </c>
+      <c r="N11" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="O11" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="P11" s="88" t="s">
         <v>115</v>
       </c>
-      <c r="M11" s="74">
-        <v>10</v>
-      </c>
-      <c r="N11" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="O11" s="74" t="s">
-        <v>63</v>
-      </c>
-      <c r="P11" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q11" s="43"/>
+      <c r="Q11" s="65"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="66"/>
-      <c r="C12" s="69"/>
+      <c r="B12" s="79"/>
+      <c r="C12" s="82"/>
       <c r="D12" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G12" s="11">
         <v>3</v>
@@ -2516,36 +2509,36 @@
         <v>3</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K12" s="15">
         <v>6</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="M12" s="16">
         <v>10</v>
       </c>
       <c r="N12" s="16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="P12" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q12" s="43"/>
+        <v>59</v>
+      </c>
+      <c r="P12" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q12" s="65"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="66"/>
-      <c r="C13" s="69"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="82"/>
       <c r="D13" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G13" s="11">
         <v>4</v>
@@ -2554,36 +2547,36 @@
         <v>4</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K13" s="15">
         <v>3</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M13" s="16">
         <v>-0.01</v>
       </c>
       <c r="N13" s="16" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="O13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="P13" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="P13" s="56" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q13" s="43"/>
+      <c r="Q13" s="65"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="66"/>
-      <c r="C14" s="69"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="82"/>
       <c r="D14" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G14" s="11">
         <v>5</v>
@@ -2592,78 +2585,78 @@
         <v>5</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K14" s="15">
         <v>2</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M14" s="16">
         <v>0</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="P14" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="P14" s="56" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q14" s="43"/>
+      <c r="Q14" s="65"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="67"/>
-      <c r="C15" s="70"/>
+      <c r="B15" s="80"/>
+      <c r="C15" s="83"/>
       <c r="D15" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G15" s="35">
         <v>6</v>
       </c>
-      <c r="H15" s="72">
+      <c r="H15" s="40">
         <v>6</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="K15" s="73">
+        <v>104</v>
+      </c>
+      <c r="K15" s="41">
         <v>1</v>
       </c>
-      <c r="L15" s="74" t="s">
-        <v>117</v>
-      </c>
-      <c r="M15" s="74">
+      <c r="L15" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="M15" s="42">
         <v>0.01</v>
       </c>
-      <c r="N15" s="74" t="s">
-        <v>53</v>
-      </c>
-      <c r="O15" s="74" t="s">
-        <v>54</v>
-      </c>
-      <c r="P15" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q15" s="43"/>
+      <c r="N15" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="O15" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="P15" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q15" s="65"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="50">
+      <c r="B16" s="67">
         <v>2</v>
       </c>
-      <c r="C16" s="50" t="s">
-        <v>59</v>
+      <c r="C16" s="67" t="s">
+        <v>55</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G16" s="11">
         <v>7</v>
@@ -2672,36 +2665,36 @@
         <v>7</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K16" s="15">
         <v>4</v>
       </c>
-      <c r="L16" s="74" t="s">
-        <v>117</v>
-      </c>
-      <c r="M16" s="74">
+      <c r="L16" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="M16" s="42">
         <v>1</v>
       </c>
-      <c r="N16" s="74" t="s">
-        <v>53</v>
-      </c>
-      <c r="O16" s="74" t="s">
-        <v>54</v>
-      </c>
-      <c r="P16" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q16" s="43"/>
+      <c r="N16" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="O16" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="P16" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q16" s="65"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="67"/>
       <c r="D17" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G17" s="11">
         <v>8</v>
@@ -2711,83 +2704,103 @@
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="K17" s="37">
         <v>101</v>
       </c>
       <c r="L17" s="38" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M17" s="38">
         <v>10</v>
       </c>
       <c r="N17" s="38" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="O17" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="P17" s="60" t="s">
+        <v>59</v>
+      </c>
+      <c r="P17" s="89" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q17" s="90"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B19" s="67"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B20" s="67"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B21" s="67"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="Q17" s="61"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B21" s="50"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B22" s="50"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="71" t="s">
-        <v>127</v>
-      </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="G28" s="63"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="40"/>
+      <c r="G28" s="85"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="62"/>
+      <c r="M28" s="62"/>
       <c r="N28" s="19"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="I29" s="62"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="62"/>
+      <c r="M29" s="62"/>
       <c r="N29" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="K8:O8"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="G7:Q7"/>
+    <mergeCell ref="I8:I9"/>
     <mergeCell ref="B9:B15"/>
     <mergeCell ref="C9:C15"/>
     <mergeCell ref="C16:C22"/>
@@ -2795,26 +2808,6 @@
     <mergeCell ref="I29:M29"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="I28:M28"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="G7:Q7"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="K8:O8"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="G8:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2842,20 +2835,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="65"/>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
       <c r="H2" s="28"/>
       <c r="I2" s="28" t="s">
         <v>3</v>
@@ -2873,7 +2866,7 @@
         <v>5</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J3" s="28">
         <v>234</v>
@@ -2888,7 +2881,7 @@
         <v>6</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J4" s="28">
         <v>234</v>
@@ -2903,374 +2896,374 @@
         <v>7</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J5" s="28">
         <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="112" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="113"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="113"/>
+      <c r="I7" s="113"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="113"/>
+    </row>
+    <row r="8" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="119" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="123" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="76"/>
-      <c r="I7" s="76"/>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
-      <c r="L7" s="76"/>
-    </row>
-    <row r="8" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="82" t="s">
+      <c r="F8" s="116" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="118"/>
+      <c r="K8" s="116" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="117"/>
+    </row>
+    <row r="9" spans="2:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="120"/>
+      <c r="C9" s="120"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="13" t="s">
         <v>77</v>
-      </c>
-      <c r="C8" s="82" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="83" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="84" t="s">
-        <v>80</v>
-      </c>
-      <c r="F8" s="79" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="79" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="80"/>
-    </row>
-    <row r="9" spans="2:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="91"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6">
         <v>1</v>
       </c>
-      <c r="C10" s="93" t="s">
-        <v>82</v>
+      <c r="C10" s="109" t="s">
+        <v>78</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F10" s="35">
         <v>1</v>
       </c>
-      <c r="G10" s="96" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="96">
+      <c r="G10" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="48">
         <v>12.5</v>
       </c>
-      <c r="I10" s="96" t="s">
-        <v>47</v>
-      </c>
-      <c r="J10" s="96" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10" s="96" t="s">
-        <v>49</v>
-      </c>
-      <c r="L10" s="98" t="s">
-        <v>49</v>
+      <c r="I10" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" s="50" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="6">
         <v>2</v>
       </c>
-      <c r="C11" s="94"/>
+      <c r="C11" s="110"/>
       <c r="D11" s="35" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F11" s="35">
         <v>2</v>
       </c>
-      <c r="G11" s="97" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" s="97">
+      <c r="G11" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="49">
         <v>10</v>
       </c>
-      <c r="I11" s="97" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="K11" s="97" t="s">
-        <v>55</v>
-      </c>
-      <c r="L11" s="98" t="s">
-        <v>55</v>
+      <c r="I11" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="50" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="6">
         <v>3</v>
       </c>
-      <c r="C12" s="94"/>
+      <c r="C12" s="110"/>
       <c r="D12" s="35" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F12" s="35">
         <v>3</v>
       </c>
-      <c r="G12" s="97" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="97">
+      <c r="G12" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="49">
         <v>-5</v>
       </c>
-      <c r="I12" s="97" t="s">
-        <v>53</v>
-      </c>
-      <c r="J12" s="97" t="s">
+      <c r="I12" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="K12" s="97" t="s">
-        <v>58</v>
-      </c>
-      <c r="L12" s="98" t="s">
-        <v>58</v>
+      <c r="L12" s="50" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="6">
         <v>4</v>
       </c>
-      <c r="C13" s="94"/>
+      <c r="C13" s="110"/>
       <c r="D13" s="35" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F13" s="35">
         <v>4</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H13" s="35">
         <v>0</v>
       </c>
       <c r="I13" s="35" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J13" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="K13" s="99" t="s">
-        <v>64</v>
-      </c>
-      <c r="L13" s="98" t="s">
-        <v>64</v>
+        <v>59</v>
+      </c>
+      <c r="K13" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="50" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="6">
         <v>5</v>
       </c>
-      <c r="C14" s="94"/>
+      <c r="C14" s="110"/>
       <c r="D14" s="35" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F14" s="35">
         <v>7</v>
       </c>
-      <c r="G14" s="97"/>
-      <c r="H14" s="97">
+      <c r="G14" s="49"/>
+      <c r="H14" s="49">
         <v>10</v>
       </c>
-      <c r="I14" s="97" t="s">
-        <v>114</v>
-      </c>
-      <c r="J14" s="97" t="s">
-        <v>63</v>
-      </c>
-      <c r="K14" s="98" t="s">
-        <v>55</v>
-      </c>
-      <c r="L14" s="98" t="s">
-        <v>55</v>
+      <c r="I14" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="L14" s="50" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="6">
         <v>6</v>
       </c>
-      <c r="C15" s="94"/>
+      <c r="C15" s="110"/>
       <c r="D15" s="35" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F15" s="35">
         <v>5</v>
       </c>
-      <c r="G15" s="97" t="s">
+      <c r="G15" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="H15" s="49">
+        <v>10</v>
+      </c>
+      <c r="I15" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="K15" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="H15" s="97">
-        <v>10</v>
-      </c>
-      <c r="I15" s="97" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" s="97" t="s">
-        <v>63</v>
-      </c>
-      <c r="K15" s="98" t="s">
-        <v>119</v>
-      </c>
-      <c r="L15" s="98" t="s">
-        <v>119</v>
+      <c r="L15" s="50" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="6">
         <v>7</v>
       </c>
-      <c r="C16" s="94"/>
+      <c r="C16" s="110"/>
       <c r="D16" s="35" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F16" s="35">
         <v>6</v>
       </c>
-      <c r="G16" s="97" t="s">
-        <v>116</v>
-      </c>
-      <c r="H16" s="97">
+      <c r="G16" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="H16" s="49">
         <v>10</v>
       </c>
-      <c r="I16" s="97" t="s">
-        <v>62</v>
-      </c>
-      <c r="J16" s="97" t="s">
-        <v>63</v>
-      </c>
-      <c r="K16" s="98" t="s">
-        <v>119</v>
-      </c>
-      <c r="L16" s="98" t="s">
-        <v>119</v>
+      <c r="I16" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="K16" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="L16" s="50" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="6">
         <v>8</v>
       </c>
-      <c r="C17" s="94"/>
+      <c r="C17" s="110"/>
       <c r="D17" s="35" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F17" s="35">
         <v>3</v>
       </c>
-      <c r="G17" s="97" t="s">
-        <v>117</v>
-      </c>
-      <c r="H17" s="97">
+      <c r="G17" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="49">
         <v>-0.01</v>
       </c>
-      <c r="I17" s="97" t="s">
-        <v>53</v>
-      </c>
-      <c r="J17" s="97" t="s">
+      <c r="I17" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="K17" s="98" t="s">
-        <v>58</v>
-      </c>
-      <c r="L17" s="98" t="s">
-        <v>58</v>
+      <c r="L17" s="50" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6">
         <v>9</v>
       </c>
-      <c r="C18" s="94"/>
+      <c r="C18" s="110"/>
       <c r="D18" s="35" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F18" s="35">
         <v>2</v>
       </c>
-      <c r="G18" s="97" t="s">
-        <v>117</v>
-      </c>
-      <c r="H18" s="97">
+      <c r="G18" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="49">
         <v>0</v>
       </c>
-      <c r="I18" s="97" t="s">
-        <v>118</v>
-      </c>
-      <c r="J18" s="97" t="s">
+      <c r="I18" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="K18" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="K18" s="98" t="s">
-        <v>58</v>
-      </c>
-      <c r="L18" s="98" t="s">
-        <v>58</v>
+      <c r="L18" s="50" t="s">
+        <v>54</v>
       </c>
       <c r="M18" s="14"/>
     </row>
@@ -3278,226 +3271,226 @@
       <c r="B19" s="6">
         <v>10</v>
       </c>
-      <c r="C19" s="94"/>
+      <c r="C19" s="110"/>
       <c r="D19" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="35" t="s">
         <v>84</v>
-      </c>
-      <c r="E19" s="35" t="s">
-        <v>88</v>
       </c>
       <c r="F19" s="35">
         <v>1</v>
       </c>
-      <c r="G19" s="97" t="s">
-        <v>117</v>
-      </c>
-      <c r="H19" s="97">
+      <c r="G19" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="H19" s="49">
         <v>0.01</v>
       </c>
-      <c r="I19" s="97" t="s">
-        <v>53</v>
-      </c>
-      <c r="J19" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="K19" s="98" t="s">
-        <v>119</v>
-      </c>
-      <c r="L19" s="98" t="s">
-        <v>119</v>
+      <c r="I19" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="L19" s="50" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="6">
         <v>11</v>
       </c>
-      <c r="C20" s="95"/>
+      <c r="C20" s="111"/>
       <c r="D20" s="35" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F20" s="35">
         <v>4</v>
       </c>
-      <c r="G20" s="97" t="s">
-        <v>117</v>
-      </c>
-      <c r="H20" s="97">
+      <c r="G20" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20" s="49">
         <v>1</v>
       </c>
-      <c r="I20" s="97" t="s">
-        <v>53</v>
-      </c>
-      <c r="J20" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="K20" s="98" t="s">
-        <v>119</v>
-      </c>
-      <c r="L20" s="98" t="s">
-        <v>119</v>
+      <c r="I20" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="J20" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="L20" s="50" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="2:16" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E21" s="86"/>
-      <c r="F21" s="87"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="88"/>
-      <c r="J21" s="88"/>
-      <c r="K21" s="90"/>
-      <c r="L21" s="86"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="43"/>
     </row>
     <row r="22" spans="2:16" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="43"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="43"/>
+    </row>
+    <row r="23" spans="2:16" s="34" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E23" s="43"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="43"/>
+    </row>
+    <row r="24" spans="2:16" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="52"/>
+      <c r="C24" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="105"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="106"/>
+      <c r="G24" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="103" t="s">
+        <v>89</v>
+      </c>
+      <c r="I24" s="104"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="103" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="86"/>
-      <c r="F22" s="87"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="88"/>
-      <c r="J22" s="88"/>
-      <c r="K22" s="90"/>
-      <c r="L22" s="86"/>
-    </row>
-    <row r="23" spans="2:16" s="34" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E23" s="86"/>
-      <c r="F23" s="87"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="88"/>
-      <c r="K23" s="90"/>
-      <c r="L23" s="86"/>
-    </row>
-    <row r="24" spans="2:16" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="101"/>
-      <c r="C24" s="110" t="s">
+      <c r="N24" s="104"/>
+      <c r="O24" s="105"/>
+      <c r="P24" s="106"/>
+    </row>
+    <row r="25" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="95" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="96" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="112"/>
-      <c r="E24" s="112"/>
-      <c r="F24" s="113"/>
-      <c r="G24" s="104" t="s">
+      <c r="D25" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25" s="97" t="s">
         <v>92</v>
       </c>
-      <c r="H24" s="110" t="s">
+      <c r="G25" s="102" t="s">
         <v>93</v>
       </c>
-      <c r="I24" s="111"/>
-      <c r="J24" s="112"/>
-      <c r="K24" s="112"/>
-      <c r="L24" s="113"/>
-      <c r="M24" s="110" t="s">
+      <c r="H25" s="98" t="s">
         <v>94</v>
       </c>
-      <c r="N24" s="111"/>
-      <c r="O24" s="112"/>
-      <c r="P24" s="113"/>
-    </row>
-    <row r="25" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="118" t="s">
+      <c r="I25" s="99"/>
+      <c r="J25" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="K25" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="L25" s="97" t="s">
+        <v>128</v>
+      </c>
+      <c r="M25" s="107" t="s">
+        <v>94</v>
+      </c>
+      <c r="N25" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="O25" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="P25" s="97" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B26" s="95"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="97"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="100"/>
+      <c r="I26" s="101"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="97"/>
+      <c r="M26" s="108"/>
+      <c r="N26" s="73"/>
+      <c r="O26" s="73"/>
+      <c r="P26" s="97"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B27" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="119" t="s">
+      <c r="C27" s="54">
+        <v>11</v>
+      </c>
+      <c r="D27" s="56">
+        <v>11</v>
+      </c>
+      <c r="E27" s="56">
+        <v>0</v>
+      </c>
+      <c r="F27" s="57"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="E25" s="55" t="s">
-        <v>132</v>
-      </c>
-      <c r="F25" s="100" t="s">
-        <v>96</v>
-      </c>
-      <c r="G25" s="124" t="s">
-        <v>97</v>
-      </c>
-      <c r="H25" s="120" t="s">
-        <v>98</v>
-      </c>
-      <c r="I25" s="121"/>
-      <c r="J25" s="55" t="s">
+      <c r="I27" s="94"/>
+      <c r="J27" s="53">
+        <v>0</v>
+      </c>
+      <c r="K27" s="56">
+        <v>0</v>
+      </c>
+      <c r="L27" s="57">
+        <v>0</v>
+      </c>
+      <c r="M27" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="K25" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="L25" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="M25" s="114" t="s">
-        <v>98</v>
-      </c>
-      <c r="N25" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="O25" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="P25" s="100" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B26" s="118"/>
-      <c r="C26" s="119"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="100"/>
-      <c r="G26" s="124"/>
-      <c r="H26" s="122"/>
-      <c r="I26" s="123"/>
-      <c r="J26" s="55"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="100"/>
-      <c r="M26" s="115"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="55"/>
-      <c r="P26" s="100"/>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B27" s="107" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" s="103">
+      <c r="N27" s="53">
         <v>11</v>
       </c>
-      <c r="D27" s="105">
+      <c r="O27" s="56">
         <v>11</v>
       </c>
-      <c r="E27" s="105">
-        <v>0</v>
-      </c>
-      <c r="F27" s="106"/>
-      <c r="G27" s="109"/>
-      <c r="H27" s="116" t="s">
-        <v>99</v>
-      </c>
-      <c r="I27" s="117"/>
-      <c r="J27" s="102">
-        <v>0</v>
-      </c>
-      <c r="K27" s="105">
-        <v>0</v>
-      </c>
-      <c r="L27" s="106">
-        <v>0</v>
-      </c>
-      <c r="M27" s="108" t="s">
-        <v>99</v>
-      </c>
-      <c r="N27" s="102">
-        <v>11</v>
-      </c>
-      <c r="O27" s="105">
-        <v>11</v>
-      </c>
-      <c r="P27" s="106">
+      <c r="P27" s="57">
         <v>0</v>
       </c>
     </row>
@@ -3506,25 +3499,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="H25:I26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="C10:C20"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="H24:L24"/>
-    <mergeCell ref="K25:K26"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B7:L7"/>
     <mergeCell ref="B2:F2"/>
@@ -3534,6 +3508,25 @@
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="K8:L8"/>
+    <mergeCell ref="C10:C20"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="H24:L24"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="H25:I26"/>
+    <mergeCell ref="G25:G26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
